--- a/artfynd/A 33707-2025 artfynd.xlsx
+++ b/artfynd/A 33707-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -919,6 +919,227 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128835167</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97490</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Marma gård, 1,1 km söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>666866</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6640157</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Lövsumpskog</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson, Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128835427</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92818</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Gården Försängen, 630 m VSV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>666998</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6639576</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Hällmarksbarrskog</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson, Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33707-2025 artfynd.xlsx
+++ b/artfynd/A 33707-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1140,6 +1140,270 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128838968</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92123</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Gården vid Marma, 1,2 km söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>666879</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6640020</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson, Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128838865</v>
+      </c>
+      <c r="B7" t="n">
+        <v>56907</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Gården vid Marma, 1,3 km söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>666958</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6639942</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Tallsumpskog</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson, Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33707-2025 artfynd.xlsx
+++ b/artfynd/A 33707-2025 artfynd.xlsx
@@ -924,7 +924,7 @@
         <v>128835167</v>
       </c>
       <c r="B4" t="n">
-        <v>97490</v>
+        <v>97496</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>128835427</v>
       </c>
       <c r="B5" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>128838968</v>
       </c>
       <c r="B6" t="n">
-        <v>92123</v>
+        <v>92128</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 33707-2025 artfynd.xlsx
+++ b/artfynd/A 33707-2025 artfynd.xlsx
@@ -924,7 +924,7 @@
         <v>128835167</v>
       </c>
       <c r="B4" t="n">
-        <v>97496</v>
+        <v>97503</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>128835427</v>
       </c>
       <c r="B5" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>128838968</v>
       </c>
       <c r="B6" t="n">
-        <v>92128</v>
+        <v>92133</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 33707-2025 artfynd.xlsx
+++ b/artfynd/A 33707-2025 artfynd.xlsx
@@ -1131,7 +1131,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Thorleif Joelson, Henry Åkerström</t>
+          <t>Henry Åkerström, Thorleif Joelson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 33707-2025 artfynd.xlsx
+++ b/artfynd/A 33707-2025 artfynd.xlsx
@@ -1131,7 +1131,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Henry Åkerström, Thorleif Joelson</t>
+          <t>Thorleif Joelson, Henry Åkerström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 33707-2025 artfynd.xlsx
+++ b/artfynd/A 33707-2025 artfynd.xlsx
@@ -924,7 +924,7 @@
         <v>128835167</v>
       </c>
       <c r="B4" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>128835427</v>
       </c>
       <c r="B5" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>128838968</v>
       </c>
       <c r="B6" t="n">
-        <v>92133</v>
+        <v>92137</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>128838865</v>
       </c>
       <c r="B7" t="n">
-        <v>56907</v>
+        <v>56910</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 33707-2025 artfynd.xlsx
+++ b/artfynd/A 33707-2025 artfynd.xlsx
@@ -924,7 +924,7 @@
         <v>128835167</v>
       </c>
       <c r="B4" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>128835427</v>
       </c>
       <c r="B5" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>128838968</v>
       </c>
       <c r="B6" t="n">
-        <v>92137</v>
+        <v>92142</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>128838865</v>
       </c>
       <c r="B7" t="n">
-        <v>56910</v>
+        <v>56913</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 33707-2025 artfynd.xlsx
+++ b/artfynd/A 33707-2025 artfynd.xlsx
@@ -924,7 +924,7 @@
         <v>128835167</v>
       </c>
       <c r="B4" t="n">
-        <v>97522</v>
+        <v>97527</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>128835427</v>
       </c>
       <c r="B5" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>128838968</v>
       </c>
       <c r="B6" t="n">
-        <v>92150</v>
+        <v>92155</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 33707-2025 artfynd.xlsx
+++ b/artfynd/A 33707-2025 artfynd.xlsx
@@ -924,7 +924,7 @@
         <v>128835167</v>
       </c>
       <c r="B4" t="n">
-        <v>97527</v>
+        <v>97530</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>128835427</v>
       </c>
       <c r="B5" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>128838968</v>
       </c>
       <c r="B6" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 33707-2025 artfynd.xlsx
+++ b/artfynd/A 33707-2025 artfynd.xlsx
@@ -1021,7 +1021,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Thorleif Joelson, Henry Åkerström</t>
+          <t>Henry Åkerström, Thorleif Joelson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 33707-2025 artfynd.xlsx
+++ b/artfynd/A 33707-2025 artfynd.xlsx
@@ -1021,7 +1021,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Henry Åkerström, Thorleif Joelson</t>
+          <t>Thorleif Joelson, Henry Åkerström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 33707-2025 artfynd.xlsx
+++ b/artfynd/A 33707-2025 artfynd.xlsx
@@ -924,7 +924,7 @@
         <v>128835167</v>
       </c>
       <c r="B4" t="n">
-        <v>97530</v>
+        <v>97540</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>128835427</v>
       </c>
       <c r="B5" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>128838968</v>
       </c>
       <c r="B6" t="n">
-        <v>92158</v>
+        <v>92165</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>128838865</v>
       </c>
       <c r="B7" t="n">
-        <v>56913</v>
+        <v>56915</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 33707-2025 artfynd.xlsx
+++ b/artfynd/A 33707-2025 artfynd.xlsx
@@ -924,7 +924,7 @@
         <v>128835167</v>
       </c>
       <c r="B4" t="n">
-        <v>97540</v>
+        <v>97547</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>128835427</v>
       </c>
       <c r="B5" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>128838968</v>
       </c>
       <c r="B6" t="n">
-        <v>92165</v>
+        <v>92172</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 33707-2025 artfynd.xlsx
+++ b/artfynd/A 33707-2025 artfynd.xlsx
@@ -924,7 +924,7 @@
         <v>128835167</v>
       </c>
       <c r="B4" t="n">
-        <v>97547</v>
+        <v>97549</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>128835427</v>
       </c>
       <c r="B5" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>128838968</v>
       </c>
       <c r="B6" t="n">
-        <v>92172</v>
+        <v>92174</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>128838865</v>
       </c>
       <c r="B7" t="n">
-        <v>56915</v>
+        <v>56917</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 33707-2025 artfynd.xlsx
+++ b/artfynd/A 33707-2025 artfynd.xlsx
@@ -924,7 +924,7 @@
         <v>128835167</v>
       </c>
       <c r="B4" t="n">
-        <v>97549</v>
+        <v>97575</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>128835427</v>
       </c>
       <c r="B5" t="n">
-        <v>92871</v>
+        <v>92857</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>128838968</v>
       </c>
       <c r="B6" t="n">
-        <v>92174</v>
+        <v>92189</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 33707-2025 artfynd.xlsx
+++ b/artfynd/A 33707-2025 artfynd.xlsx
@@ -924,7 +924,7 @@
         <v>128835167</v>
       </c>
       <c r="B4" t="n">
-        <v>97575</v>
+        <v>97576</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>128835427</v>
       </c>
       <c r="B5" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>128838968</v>
       </c>
       <c r="B6" t="n">
-        <v>92189</v>
+        <v>92190</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Thorleif Joelson, Henry Åkerström</t>
+          <t>Henry Åkerström, Thorleif Joelson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">

--- a/artfynd/A 33707-2025 artfynd.xlsx
+++ b/artfynd/A 33707-2025 artfynd.xlsx
@@ -924,7 +924,7 @@
         <v>128835167</v>
       </c>
       <c r="B4" t="n">
-        <v>97576</v>
+        <v>97577</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Henry Åkerström, Thorleif Joelson</t>
+          <t>Thorleif Joelson, Henry Åkerström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">

--- a/artfynd/A 33707-2025 artfynd.xlsx
+++ b/artfynd/A 33707-2025 artfynd.xlsx
@@ -1145,7 +1145,7 @@
         <v>128838968</v>
       </c>
       <c r="B6" t="n">
-        <v>92190</v>
+        <v>92193</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
